--- a/data/trans_dic/P64D$particular_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P64D$particular_2023-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en vehículo particular (automóvil, moto)</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en vehículo particular (automóvil, moto) (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>77,05; 85,75</t>
+          <t>77,65; 86,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>60,56; 69,86</t>
+          <t>60,0; 70,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71,02; 77,95</t>
+          <t>71,24; 78,18</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>75,46; 93,47</t>
+          <t>75,14; 93,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>60,2; 68,48</t>
+          <t>60,59; 68,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70,65; 87,49</t>
+          <t>70,77; 87,84</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>76,0; 85,35</t>
+          <t>75,69; 85,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>71,35; 83,11</t>
+          <t>71,23; 83,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>75,26; 82,74</t>
+          <t>75,3; 82,67</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>58,08; 66,97</t>
+          <t>57,31; 66,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,75; 51,0</t>
+          <t>24,85; 51,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38,1; 57,87</t>
+          <t>40,15; 57,9</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>74,16; 85,11</t>
+          <t>73,96; 84,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>50,57; 64,29</t>
+          <t>50,31; 64,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65,66; 76,61</t>
+          <t>65,89; 75,8</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en vehículo particular (automóvil, moto)</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en vehículo particular (automóvil, moto) (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>256650; 285619</t>
+          <t>258646; 286438</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>156292; 180296</t>
+          <t>154829; 181607</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>419829; 460771</t>
+          <t>421118; 462166</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>607854; 752896</t>
+          <t>605249; 750893</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>241320; 274538</t>
+          <t>242903; 276202</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>852247; 1055500</t>
+          <t>853704; 1059696</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>270595; 303874</t>
+          <t>269471; 304652</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>230015; 267936</t>
+          <t>229628; 269768</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>510579; 561309</t>
+          <t>510845; 560856</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>273594; 315479</t>
+          <t>269987; 314941</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>128270; 244584</t>
+          <t>119159; 245855</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>362243; 550196</t>
+          <t>381739; 550466</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1457763; 1673040</t>
+          <t>1453831; 1670403</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>738808; 939288</t>
+          <t>735063; 936876</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2249815; 2625071</t>
+          <t>2257817; 2597394</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P64D$particular_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P64D$particular_2023-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>73,86%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>77,65; 86,0</t>
+          <t>75,07; 84,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>60,0; 70,37</t>
+          <t>60,87; 70,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71,24; 78,18</t>
+          <t>70,55; 77,16</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>70,01%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>75,14; 93,22</t>
+          <t>70,73; 78,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>60,59; 68,9</t>
+          <t>58,75; 67,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70,77; 87,84</t>
+          <t>66,82; 72,89</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>76,26%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>75,69; 85,57</t>
+          <t>75,0; 84,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>71,23; 83,68</t>
+          <t>66,73; 75,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>75,3; 82,67</t>
+          <t>72,59; 79,43</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>54,22%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>57,31; 66,85</t>
+          <t>55,13; 64,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,85; 51,26</t>
+          <t>43,53; 51,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40,15; 57,9</t>
+          <t>51,33; 57,37</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>67,68%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>73,96; 84,98</t>
+          <t>70,66; 75,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>50,31; 64,13</t>
+          <t>58,52; 63,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65,89; 75,8</t>
+          <t>66,02; 69,3</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>273113</t>
+          <t>292985</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>169098</t>
+          <t>184039</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>442210</t>
+          <t>477025</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>258646; 286438</t>
+          <t>275379; 308280</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>154829; 181607</t>
+          <t>169825; 196642</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>421118; 462166</t>
+          <t>455646; 498358</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>674916</t>
+          <t>469058</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>260185</t>
+          <t>283608</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>935100</t>
+          <t>752666</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>605249; 750893</t>
+          <t>444208; 493286</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>242903; 276202</t>
+          <t>262646; 300842</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>853704; 1059696</t>
+          <t>718434; 783643</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>288774</t>
+          <t>335750</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>246432</t>
+          <t>240123</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>535206</t>
+          <t>575872</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>269471; 304652</t>
+          <t>313168; 353029</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>229628; 269768</t>
+          <t>225247; 255936</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>510845; 560856</t>
+          <t>548156; 599767</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>294522</t>
+          <t>310213</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>204095</t>
+          <t>212679</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>498617</t>
+          <t>522892</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>269987; 314941</t>
+          <t>284853; 333434</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>119159; 245855</t>
+          <t>194859; 231408</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>381739; 550466</t>
+          <t>495064; 553310</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1531325</t>
+          <t>1408006</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>879809</t>
+          <t>920448</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2411135</t>
+          <t>2328455</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1453831; 1670403</t>
+          <t>1363077; 1449760</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>735063; 936876</t>
+          <t>884410; 953875</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2257817; 2597394</t>
+          <t>2271399; 2384275</t>
         </is>
       </c>
     </row>
